--- a/blog/posts/2026-07_war_two_inflation/out/war_two_inflation_data.xlsx
+++ b/blog/posts/2026-07_war_two_inflation/out/war_two_inflation_data.xlsx
@@ -17,6 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6_Consumer" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7_Labor" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S8_EPU" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10_LaborSupply" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S11_LaborComp" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +415,529 @@
                 </a:pPr>
                 <a:r>
                   <a:t>idx</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>고용률 · 참가율 (%)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'S10_LaborSupply'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S10_LaborSupply'!$A$4:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S10_LaborSupply'!$C$4:$C$32</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'S10_LaborSupply'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S10_LaborSupply'!$A$4:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S10_LaborSupply'!$D$4:$D$32</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'S10_LaborSupply'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S10_LaborSupply'!$A$4:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S10_LaborSupply'!$E$4:$E$32</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="yyyy-mm" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>실업률 U-3 (%)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'S10_LaborSupply'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S10_LaborSupply'!$A$4:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S10_LaborSupply'!$B$4:$B$32</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="yyyy-mm" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>노동력 수준(천명) — 총계 SA / 외국인 NSA</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'S11_LaborComp'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S11_LaborComp'!$A$4:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S11_LaborComp'!$B$4:$B$28</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'S11_LaborComp'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S11_LaborComp'!$A$4:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S11_LaborComp'!$C$4:$C$28</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="yyyy-mm" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>천명</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>시간당 임금 YoY(%)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'S11_LaborComp'!G3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'S11_LaborComp'!$A$4:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'S11_LaborComp'!$G$4:$G$28</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="yyyy-mm" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1422,6 +1947,104 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1949,15 +2572,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2056,7 +2679,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>PCEPILFE·CPIAUCSL·CPILFESL</t>
+          <t>PCEPILFE(SA)·CPIAUCNS·CPILFENS(NSA)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2066,7 +2689,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>CPI=NSA(CPIAUCNS·CPILFENS), 공식 보도치 일치</t>
+          <t>Core PCE는 SA, CPI는 NSA(BLS 공식 보도치와 일치) — 조정방식이 다르다</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2881,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>4.2% / +57k</t>
+          <t>4.2% / +57k — 해석은 S10 참조</t>
         </is>
       </c>
     </row>
@@ -2294,22 +2917,86 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>S10_LaborSupply</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>실업률·고용률·참가율</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>UNRATE·EMRATIO·CIVPART·LNS11300060·U6RATE(SA)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>분모(참가율) 축소 분해 — 반사실은 차트에서 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>S11_LaborComp</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>노동력 구성·시급</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>CLF16OV·LNU01073395·LNU01373395·NILFWJN·CES0500000003</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>외국인 LF·LFPR은 NSA · 26년 1월 인구통제 재벤치마킹 단절 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>주석/이벤트(annotations.json):</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SEP 2026 median 3.8% · SPR 계획 172M/실제 17.5M · 유가피크 Brent 138.21(4/7)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t>SEP 2026 median 3.8% · SPR 계획 172M/실제 17.5M · 유가피크 Brent 138.21(4/7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>이벤트: 2026-02-28 US-Iran 개전 / 2026-04-08 휴전 / 2026-07-08 재점화(미국 타격)</t>
         </is>
@@ -2335,6 +3022,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3741,6 +4430,1416 @@
       </c>
       <c r="B141" t="n">
         <v>198.04987</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>⑩ 노동공급 분해 (실업률 · 고용률 · 참가율)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2025-11 → 2026-06: 실업률 4.5→4.2%인데 고용률도 59.6→59.0% · 참가율 62.5→61.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>unrate</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>emratio</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>civpart</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>primeage_civpart</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>u6rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v/>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v/>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v/>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v/>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v/>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v/>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v/>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v/>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v/>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v/>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v/>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v/>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>60</v>
+      </c>
+      <c r="D19" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v/>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v/>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>84</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>62</v>
+      </c>
+      <c r="E28" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>59</v>
+      </c>
+      <c r="D32" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>⑪ 노동력 구성 · 시급</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>총 노동력 -1,022k 중 외국인 -700k(68%) · 단 외국인 LFPR도 66.3→65.6 · AHE YoY 3.86→3.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>clf_total_sa_k</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>clf_foreignborn_nsa_k</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>foreignborn_lfpr_nsa</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>nilf_want_job_k</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>ahe_usd</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>ahe_yoy_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>168034</v>
+      </c>
+      <c r="C4" t="n">
+        <v>32224</v>
+      </c>
+      <c r="D4" t="n">
+        <v>67</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5232</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>168395</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32518</v>
+      </c>
+      <c r="D5" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5605</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>168492</v>
+      </c>
+      <c r="C6" t="n">
+        <v>33049</v>
+      </c>
+      <c r="D6" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5600</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>168662</v>
+      </c>
+      <c r="C7" t="n">
+        <v>32781</v>
+      </c>
+      <c r="D7" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5740</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>168395</v>
+      </c>
+      <c r="C8" t="n">
+        <v>32435</v>
+      </c>
+      <c r="D8" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5662</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>168248</v>
+      </c>
+      <c r="C9" t="n">
+        <v>32272</v>
+      </c>
+      <c r="D9" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5498</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>168506</v>
+      </c>
+      <c r="C10" t="n">
+        <v>32101</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5524</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>170696</v>
+      </c>
+      <c r="C11" t="n">
+        <v>33307</v>
+      </c>
+      <c r="D11" t="n">
+        <v>66</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5506</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>170441</v>
+      </c>
+      <c r="C12" t="n">
+        <v>33241</v>
+      </c>
+      <c r="D12" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5896</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>170641</v>
+      </c>
+      <c r="C13" t="n">
+        <v>33719</v>
+      </c>
+      <c r="D13" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5910</v>
+      </c>
+      <c r="F13" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>171054</v>
+      </c>
+      <c r="C14" t="n">
+        <v>33004</v>
+      </c>
+      <c r="D14" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5691</v>
+      </c>
+      <c r="F14" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>170492</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32706</v>
+      </c>
+      <c r="D15" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6008</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>170380</v>
+      </c>
+      <c r="C16" t="n">
+        <v>32572</v>
+      </c>
+      <c r="D16" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6032</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>170412</v>
+      </c>
+      <c r="C17" t="n">
+        <v>32066</v>
+      </c>
+      <c r="D17" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6186</v>
+      </c>
+      <c r="F17" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>170750</v>
+      </c>
+      <c r="C18" t="n">
+        <v>32239</v>
+      </c>
+      <c r="D18" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6347</v>
+      </c>
+      <c r="F18" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>171261</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32073</v>
+      </c>
+      <c r="D19" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5943</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v/>
+      </c>
+      <c r="C20" t="n">
+        <v/>
+      </c>
+      <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
+        <v/>
+      </c>
+      <c r="F20" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>171541</v>
+      </c>
+      <c r="C21" t="n">
+        <v>32205</v>
+      </c>
+      <c r="D21" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6139</v>
+      </c>
+      <c r="F21" t="n">
+        <v>37</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>171495</v>
+      </c>
+      <c r="C22" t="n">
+        <v>32426</v>
+      </c>
+      <c r="D22" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6208</v>
+      </c>
+      <c r="F22" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>170465</v>
+      </c>
+      <c r="C23" t="n">
+        <v>33058</v>
+      </c>
+      <c r="D23" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5838</v>
+      </c>
+      <c r="F23" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>170483</v>
+      </c>
+      <c r="C24" t="n">
+        <v>32711</v>
+      </c>
+      <c r="D24" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5974</v>
+      </c>
+      <c r="F24" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>170087</v>
+      </c>
+      <c r="C25" t="n">
+        <v>33401</v>
+      </c>
+      <c r="D25" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6040</v>
+      </c>
+      <c r="F25" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>169995</v>
+      </c>
+      <c r="C26" t="n">
+        <v>32851</v>
+      </c>
+      <c r="D26" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6111</v>
+      </c>
+      <c r="F26" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>170078</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32612</v>
+      </c>
+      <c r="D27" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6187</v>
+      </c>
+      <c r="F27" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>169358</v>
+      </c>
+      <c r="C28" t="n">
+        <v>31872</v>
+      </c>
+      <c r="D28" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6045</v>
+      </c>
+      <c r="F28" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.52</v>
       </c>
     </row>
   </sheetData>
@@ -3764,6 +5863,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20770,6 +22871,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21501,6 +23604,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23375,6 +25480,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27884,6 +29991,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28615,6 +30724,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29084,6 +31195,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29583,6 +31696,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29595,7 +31710,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>4.2% / +57k — 완충</t>
+          <t>4.2% / +57k — 표면 수치. 분모 효과는 S10 시트에서 분해</t>
         </is>
       </c>
     </row>

--- a/blog/posts/2026-07_war_two_inflation/out/war_two_inflation_data.xlsx
+++ b/blog/posts/2026-07_war_two_inflation/out/war_two_inflation_data.xlsx
@@ -2572,7 +2572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>계획172M/실제17.5M(4/24)/재고397.9M=주석</t>
+          <t>주석값: 계획 172M / 4-24까지 실제 방출 17.5M / 4-24 시점 재고 397.9M — 셋 다 시계열이 아니라 주석</t>
         </is>
       </c>
     </row>
@@ -2977,26 +2977,58 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>외국인 LF·LFPR은 NSA · 26년 1월 인구통제 재벤치마킹 단절 주의</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+          <t>본문 6장(차트 ⑩)의 뒷받침 자료다 — 차트 ⑪이 아니다 · 외국인 LF·LFPR은 NSA · 26년 1월 인구통제 재벤치마킹 단절 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>(시트 없음)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>차트 ⑨ 대시보드 / 차트 ⑪ Core PCE−Core CPI 웨지</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>⑨는 다른 시트값의 요약, ⑪은 S2_Inflation의 두 열 차분이라 별도 원자료가 없다. 시트 번호와 차트 번호가 1:1이 아닌 지점은 이 둘뿐이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>주석/이벤트(annotations.json):</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SEP 2026 median 3.8% · SPR 계획 172M/실제 17.5M · 유가피크 Brent 138.21(4/7)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>SEP 2026 median 3.8% · SPR 계획 172M/실제 17.5M · 유가피크 Brent 138.21(4/7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>이벤트: 2026-02-28 US-Iran 개전 / 2026-04-08 휴전 / 2026-07-08 재점화(미국 타격)</t>
         </is>
@@ -5176,7 +5208,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>총 노동력 -1,022k 중 외국인 -700k(68%) · 단 외국인 LFPR도 66.3→65.6 · AHE YoY 3.86→3.52%</t>
+          <t>총 노동력 -1,022k(SA) · 외국인 -700k(NSA) — 조정방식이 달라 기여율로 나누지 않는다 · 외국인 LFPR 66.3→65.6 · AHE YoY 3.86→3.52%</t>
         </is>
       </c>
     </row>
